--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/ago-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/ago-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ago-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ago-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17080,7 +17080,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17690,7 +17690,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17812,7 +17812,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19093,7 +19093,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19337,7 +19337,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19459,7 +19459,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20557,7 +20557,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20618,7 +20618,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -20679,7 +20679,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21045,7 +21045,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21228,7 +21228,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21411,7 +21411,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21594,7 +21594,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21777,7 +21777,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22265,7 +22265,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22448,7 +22448,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22570,7 +22570,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23729,7 +23729,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -23790,7 +23790,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23851,7 +23851,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24034,7 +24034,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24156,7 +24156,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24217,7 +24217,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24583,7 +24583,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -24888,7 +24888,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -25010,7 +25010,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -25193,7 +25193,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -25315,7 +25315,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25559,7 +25559,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -25620,7 +25620,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -25681,7 +25681,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -25803,7 +25803,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -25925,7 +25925,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -25986,7 +25986,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -26108,7 +26108,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26230,7 +26230,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -26352,7 +26352,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -26657,7 +26657,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -26779,7 +26779,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -26840,7 +26840,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27328,7 +27328,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -27450,7 +27450,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -27572,7 +27572,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -27694,7 +27694,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -27816,7 +27816,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -27938,7 +27938,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28121,7 +28121,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28182,7 +28182,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28243,7 +28243,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28365,7 +28365,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -28426,7 +28426,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -28487,7 +28487,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28548,7 +28548,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -28609,7 +28609,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28670,7 +28670,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -28731,7 +28731,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -28975,7 +28975,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29036,7 +29036,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29097,7 +29097,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -29219,7 +29219,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29402,7 +29402,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -29524,7 +29524,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29585,7 +29585,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -29768,7 +29768,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -29829,7 +29829,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -29890,7 +29890,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -29951,7 +29951,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30012,7 +30012,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30073,7 +30073,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30195,7 +30195,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30317,7 +30317,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -30439,7 +30439,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30622,7 +30622,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30683,7 +30683,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30805,7 +30805,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -30927,7 +30927,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -31171,7 +31171,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31232,7 +31232,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -31293,7 +31293,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31354,7 +31354,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31415,7 +31415,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -31476,7 +31476,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -31537,7 +31537,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -31598,7 +31598,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -31659,7 +31659,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31720,7 +31720,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -31781,7 +31781,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -31842,7 +31842,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -31903,7 +31903,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32025,7 +32025,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -32086,7 +32086,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32147,7 +32147,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32269,7 +32269,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32330,7 +32330,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -32391,7 +32391,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -32452,7 +32452,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -32513,7 +32513,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -32574,7 +32574,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -32635,7 +32635,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -32696,7 +32696,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -32757,7 +32757,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32879,7 +32879,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -32940,7 +32940,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33001,7 +33001,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -33062,7 +33062,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -33123,7 +33123,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -33184,7 +33184,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -33245,7 +33245,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33306,7 +33306,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -33367,7 +33367,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -33550,7 +33550,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -33611,7 +33611,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33672,7 +33672,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33733,7 +33733,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -33855,7 +33855,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -33977,7 +33977,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34160,7 +34160,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -34221,7 +34221,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -34282,7 +34282,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -34343,7 +34343,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -34404,7 +34404,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34465,7 +34465,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34587,7 +34587,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -34648,7 +34648,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34709,7 +34709,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -34770,7 +34770,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -34831,7 +34831,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -34892,7 +34892,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -34953,7 +34953,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35075,7 +35075,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35136,7 +35136,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -35197,7 +35197,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -35258,7 +35258,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35319,7 +35319,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -35380,7 +35380,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35441,7 +35441,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -35502,7 +35502,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -35563,7 +35563,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -35624,7 +35624,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -35685,7 +35685,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35746,7 +35746,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -35807,7 +35807,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -35868,7 +35868,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -35929,7 +35929,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -35990,7 +35990,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36051,7 +36051,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36112,7 +36112,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36173,7 +36173,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -36234,7 +36234,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -36295,7 +36295,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -36356,7 +36356,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -36417,7 +36417,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -36539,7 +36539,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -36600,7 +36600,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -36661,7 +36661,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -36783,7 +36783,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -36844,7 +36844,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -36905,7 +36905,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -36966,7 +36966,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37027,7 +37027,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -37088,7 +37088,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37149,7 +37149,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -37210,7 +37210,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -37271,7 +37271,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37332,7 +37332,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -37347,7 +37347,7 @@
       </c>
       <c r="K605" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L605" t="inlineStr">
@@ -37397,7 +37397,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -37458,7 +37458,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -37519,7 +37519,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -37580,7 +37580,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37702,7 +37702,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -37763,7 +37763,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -37824,7 +37824,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -37885,7 +37885,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38007,7 +38007,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -38068,7 +38068,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -38129,7 +38129,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -38190,7 +38190,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -38251,7 +38251,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -38312,7 +38312,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -38373,7 +38373,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -38434,7 +38434,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -38495,7 +38495,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -38556,7 +38556,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -38617,7 +38617,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -38800,7 +38800,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -38861,7 +38861,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -38922,7 +38922,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -38983,7 +38983,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39044,7 +39044,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -39105,7 +39105,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -39166,7 +39166,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39227,7 +39227,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -39288,7 +39288,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -39349,7 +39349,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -39410,7 +39410,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -39471,7 +39471,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -39532,7 +39532,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -39593,7 +39593,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -39654,7 +39654,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -39715,7 +39715,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -39776,7 +39776,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -39837,7 +39837,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -39898,7 +39898,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -39913,7 +39913,7 @@
       </c>
       <c r="K647" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L647" t="inlineStr">
@@ -39963,7 +39963,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -40024,7 +40024,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -40085,7 +40085,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -40146,7 +40146,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -40207,7 +40207,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -40268,7 +40268,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -40329,7 +40329,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -40390,7 +40390,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -40451,7 +40451,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -40512,7 +40512,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -40573,7 +40573,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -40634,7 +40634,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -40695,7 +40695,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -40756,7 +40756,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -40817,7 +40817,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -40878,7 +40878,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -40939,7 +40939,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -41000,7 +41000,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -41122,7 +41122,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -41183,7 +41183,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -41244,7 +41244,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -41305,7 +41305,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -41366,7 +41366,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -41427,7 +41427,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -41488,7 +41488,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -41610,7 +41610,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -41671,7 +41671,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -41732,7 +41732,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -41793,7 +41793,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -41854,7 +41854,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -41915,7 +41915,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -41976,7 +41976,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -42037,7 +42037,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -42098,7 +42098,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -42159,7 +42159,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -42220,7 +42220,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42281,7 +42281,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -42342,7 +42342,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -42403,7 +42403,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -42464,7 +42464,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -42525,7 +42525,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -42586,7 +42586,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/ago-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/ago-2025.xlsx
@@ -562,7 +562,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1196,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1322,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1387,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1635,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1761,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1887,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2013,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2139,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2204,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2269,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2334,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2399,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2464,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2651,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2838,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2903,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3090,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3155,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3220,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3285,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3350,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3476,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3541,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3606,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3671,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3736,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3801,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3866,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3992,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4057,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4122,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4248,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4313,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4378,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4443,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4508,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4573,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4760,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4825,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4890,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4955,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5081,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5146,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5211,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5276,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5341,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5589,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5776,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5963,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6211,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6337,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6524,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6711,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6837,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6902,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6967,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7032,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7097,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7162,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7349,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7475,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7540,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7605,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7792,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7857,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7922,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7987,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8113,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8178,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8304,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8369,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8495,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8560,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8625,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8751,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8877,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9003,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9068,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9133,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9198,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9263,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9328,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9454,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9519,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9645,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9710,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9836,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9962,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10027,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10092,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10157,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10344,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10409,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10474,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10783,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10848,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +10974,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11039,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11104,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11169,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11234,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11360,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11486,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11551,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11616,11 @@
           <t>77.173.807-9</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11681,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11746,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11872,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +11998,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12063,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12128,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12254,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12441,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12506,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12571,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12636,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12762,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12888,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +12953,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13079,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13205,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13392,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13457,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13583,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13648,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13713,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +13900,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +13965,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14030,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14095,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14221,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14347,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14412,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14477,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14542,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14607,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14672,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14737,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14863,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +14989,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15054,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15302,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15367,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15432,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15497,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15623,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15688,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15753,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16001,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16066,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16253,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16318,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16383,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16509,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16635,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16761,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16826,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +16952,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17017,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17204,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17269,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17334,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17460,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17586,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17651,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17716,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17842,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +17968,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18094,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18281,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18529,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +18594,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18720,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +18907,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +18972,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19098,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19163,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19289,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19354,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19419,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19484,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19549,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19675,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +19801,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20049,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20297,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20728,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20793,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +20858,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +20923,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +20988,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21114,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21240,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21305,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21614,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +21679,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +21805,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +21870,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +21935,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22122,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22370,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22435,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +22500,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +22565,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22630,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +22878,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +22943,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +23008,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23073,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +23138,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23203,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23268,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23394,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +23459,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +23524,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +23711,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +23776,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +23841,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +23906,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +23971,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23254,7 +24158,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24223,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24288,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +24414,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24479,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +24727,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23925,7 +24853,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +24918,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +24983,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +25048,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25174,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25300,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25365,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +25430,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +25495,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +25560,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +25686,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +25751,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +25816,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +25881,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +26007,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +26133,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +26198,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26263,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26328,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +26393,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +26458,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +26523,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25572,7 +26588,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +26653,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +26718,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +26844,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25877,7 +26909,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27157,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +27283,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +27470,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +27535,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27661,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +27787,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26792,7 +27852,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +27978,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28104,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28169,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28295,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27524,7 +28604,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +28730,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +28795,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +28860,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +28986,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29112,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +29177,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +29242,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +29429,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +29494,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +29559,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +29624,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +29689,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +29876,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28866,7 +30002,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28927,7 +30067,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28988,7 +30132,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30197,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29171,7 +30323,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +30449,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29354,7 +30514,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +30579,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29476,7 +30644,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29537,7 +30709,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +30835,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29842,7 +31022,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29903,7 +31087,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29964,7 +31152,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30025,7 +31217,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30269,7 +31465,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +31530,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +31595,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30452,7 +31660,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30696,7 +31908,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +31973,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30818,7 +32038,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31306,7 +32530,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31428,7 +32656,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31489,7 +32721,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31611,7 +32847,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31672,7 +32912,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31733,7 +32977,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31794,7 +33042,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31855,7 +33107,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32282,7 +33538,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32465,7 +33725,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32648,7 +33912,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32831,7 +34099,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32892,7 +34164,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32953,7 +34229,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33075,7 +34355,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33197,7 +34481,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33258,7 +34546,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33319,7 +34611,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33380,7 +34676,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33441,7 +34741,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33563,7 +34867,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33624,7 +34932,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33746,7 +35058,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33807,7 +35123,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33868,7 +35188,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33929,7 +35253,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34112,7 +35440,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34295,7 +35627,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34356,7 +35692,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34417,7 +35757,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34539,7 +35883,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34600,7 +35948,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34783,7 +36135,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34844,7 +36200,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34905,7 +36265,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35088,7 +36452,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35149,7 +36517,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35393,7 +36765,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35454,7 +36830,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35637,7 +37017,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35698,7 +37082,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35759,7 +37147,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35881,7 +37273,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36003,7 +37399,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36125,7 +37525,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36186,7 +37590,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36247,7 +37655,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36308,7 +37720,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36369,7 +37785,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36430,7 +37850,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36491,7 +37915,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36552,7 +37980,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36674,7 +38106,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36735,7 +38171,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36918,7 +38358,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36979,7 +38423,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37040,7 +38488,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37101,7 +38553,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37162,7 +38618,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37223,7 +38683,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37284,7 +38748,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37410,7 +38878,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37471,7 +38943,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37654,7 +39130,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37715,7 +39195,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37776,7 +39260,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37898,7 +39386,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37959,7 +39451,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38203,7 +39699,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38264,7 +39764,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38386,7 +39890,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38508,7 +40016,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38630,7 +40142,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38691,7 +40207,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38752,7 +40272,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38813,7 +40337,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38935,7 +40463,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38996,7 +40528,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39057,7 +40593,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39118,7 +40658,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39179,7 +40723,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39301,7 +40849,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39362,7 +40914,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39423,7 +40979,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39545,7 +41105,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39606,7 +41170,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39667,7 +41235,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39789,7 +41361,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39850,7 +41426,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39976,7 +41556,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40281,7 +41865,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40464,7 +42052,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40586,7 +42178,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40647,7 +42243,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40708,7 +42308,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40769,7 +42373,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40830,7 +42438,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40891,7 +42503,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40952,7 +42568,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41013,7 +42633,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41074,7 +42698,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41257,7 +42885,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41318,7 +42950,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41501,7 +43137,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41562,7 +43202,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41623,7 +43267,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41684,7 +43332,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41806,7 +43458,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41867,7 +43523,11 @@
           <t>76.525.922-3</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41928,7 +43588,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42050,7 +43714,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42172,7 +43840,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42233,7 +43905,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42538,7 +44214,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42599,7 +44279,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/ago-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/ago-2025.xlsx
@@ -818,7 +818,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1826,7 +1830,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2529,7 +2537,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3415,7 +3427,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4187,7 +4203,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5715,7 +5735,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5902,7 +5926,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6589,7 +6617,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6650,7 +6682,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6776,7 +6812,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9901,7 +9941,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10283,7 +10327,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10913,7 +10961,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11937,7 +11989,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +12757,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13144,7 +13204,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14286,7 +14350,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15241,7 +15309,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15562,7 +15634,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15879,7 +15955,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16131,7 +16211,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17907,7 +17991,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19614,7 +19702,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19740,7 +19832,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20175,7 +20271,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21431,7 +21531,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21553,7 +21657,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22309,7 +22417,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22695,7 +22807,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22817,7 +22933,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25946,7 +26066,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26974,7 +27098,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27222,7 +27350,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27348,7 +27480,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27600,7 +27736,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27726,7 +27866,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28421,7 +28565,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28925,7 +29073,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30774,7 +30926,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32103,7 +32259,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33355,7 +33515,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36330,7 +36494,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37338,7 +37506,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37464,7 +37636,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40081,7 +40257,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42117,7 +42297,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
